--- a/artfynd/A 64868-2021 artfynd.xlsx
+++ b/artfynd/A 64868-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64868-2021 artfynd.xlsx
+++ b/artfynd/A 64868-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112610363</v>
+        <v>112610365</v>
       </c>
       <c r="B10" t="n">
-        <v>91044</v>
+        <v>91032</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,21 +1627,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711644</v>
+        <v>711607</v>
       </c>
       <c r="R10" t="n">
-        <v>7158910</v>
+        <v>7158956</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1718,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112606563</v>
+        <v>112610364</v>
       </c>
       <c r="B11" t="n">
-        <v>91044</v>
+        <v>91026</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,25 +1730,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1758,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711641</v>
+        <v>711575</v>
       </c>
       <c r="R11" t="n">
-        <v>7158909</v>
+        <v>7158881</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112610365</v>
+        <v>112610366</v>
       </c>
       <c r="B12" t="n">
-        <v>91032</v>
+        <v>89789</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,25 +1837,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711607</v>
+        <v>711715</v>
       </c>
       <c r="R12" t="n">
-        <v>7158956</v>
+        <v>7158854</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,434 +1929,6 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>112610364</v>
-      </c>
-      <c r="B13" t="n">
-        <v>91026</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>711575</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7158881</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>112606564</v>
-      </c>
-      <c r="B14" t="n">
-        <v>91026</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>711581</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7158872</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>112610366</v>
-      </c>
-      <c r="B15" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>711715</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7158854</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>112606562</v>
-      </c>
-      <c r="B16" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>711710</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7158858</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64868-2021 artfynd.xlsx
+++ b/artfynd/A 64868-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104159891</v>
+        <v>112606564</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711710.3710449766</v>
+        <v>711581</v>
       </c>
       <c r="R2" t="n">
-        <v>7158858.397691542</v>
+        <v>7158872</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104159893</v>
+        <v>112610364</v>
       </c>
       <c r="B3" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711581.2724790375</v>
+        <v>711575</v>
       </c>
       <c r="R3" t="n">
-        <v>7158871.904722839</v>
+        <v>7158881</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,24 +845,14 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104159892</v>
+        <v>112610365</v>
       </c>
       <c r="B4" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711641.4459151649</v>
+        <v>711607</v>
       </c>
       <c r="R4" t="n">
-        <v>7158909.386102984</v>
+        <v>7158956</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,24 +947,14 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,19 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109910005</v>
+        <v>112606563</v>
       </c>
       <c r="B5" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711643.6003108795</v>
+        <v>711642</v>
       </c>
       <c r="R5" t="n">
-        <v>7158909.535949728</v>
+        <v>7158910</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1143,37 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109910009</v>
+        <v>112610363</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711715.4701018606</v>
+        <v>711643</v>
       </c>
       <c r="R6" t="n">
-        <v>7158853.563276037</v>
+        <v>7158910</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1151,9 @@
           <t>2022-09-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1257,678 +1182,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>109910004</v>
-      </c>
-      <c r="B7" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>711728.5530351156</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7158839.770821405</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>109910007</v>
-      </c>
-      <c r="B8" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>4366</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Skarp dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Hydnellum peckii</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>711575.0426130884</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7158880.552501309</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>109910008</v>
-      </c>
-      <c r="B9" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>711607.0109070733</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7158956.287007744</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>112610365</v>
-      </c>
-      <c r="B10" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>711607</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7158956</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>112610364</v>
-      </c>
-      <c r="B11" t="n">
-        <v>91026</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>711575</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7158881</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>112610366</v>
-      </c>
-      <c r="B12" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Åmsele, Vb</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>711715</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7158854</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2022-09-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64868-2021 artfynd.xlsx
+++ b/artfynd/A 64868-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606564</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610364</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610365</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606563</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610363</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>